--- a/DataTables/DetailText/剧情/000_05结局.xlsx
+++ b/DataTables/DetailText/剧情/000_05结局.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88E6DDED-846C-43BD-8D3A-6E93228BB24B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC37F77D-C8C1-4D91-92FC-02D7D1274084}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story" sheetId="3" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="41">
   <si>
     <t>LineIndex</t>
   </si>
@@ -598,6 +598,32 @@
       <t>岁…</t>
     </r>
     <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <r>
+      <t>res://Assets/Music/Story/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>寻幽探胜</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>.mp3</t>
+    </r>
+    <phoneticPr fontId="4"/>
   </si>
 </sst>
 </file>
@@ -1479,7 +1505,9 @@
       <c r="H2" s="29" t="s">
         <v>39</v>
       </c>
-      <c r="I2" s="26"/>
+      <c r="I2" s="28" t="s">
+        <v>40</v>
+      </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="1">

--- a/DataTables/DetailText/剧情/000_05结局.xlsx
+++ b/DataTables/DetailText/剧情/000_05结局.xlsx
@@ -1,35 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC37F77D-C8C1-4D91-92FC-02D7D1274084}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BDC0CDE-944B-4FB0-82F4-D48F11E3DBA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story" sheetId="3" r:id="rId1"/>
     <sheet name="StoryLine" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
@@ -479,7 +466,83 @@
   </si>
   <si>
     <r>
-      <t>res://Assets/Background/00</t>
+      <t>万</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>历</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>二十一年</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>李东璧</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>病逝，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>终</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>年76</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>岁…</t>
+    </r>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <r>
+      <t>res://Assets/Music/Story/</t>
     </r>
     <r>
       <rPr>
@@ -489,7 +552,7 @@
         <family val="3"/>
         <charset val="134"/>
       </rPr>
-      <t>0</t>
+      <t>寻幽探胜</t>
     </r>
     <r>
       <rPr>
@@ -499,130 +562,12 @@
         <family val="3"/>
         <charset val="128"/>
       </rPr>
-      <t>/000_0</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>0</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>.png</t>
-    </r>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <r>
-      <t>万</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>历</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>二十一年</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>李东璧</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>病逝，</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>终</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>年76</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>岁…</t>
-    </r>
-    <phoneticPr fontId="9"/>
-  </si>
-  <si>
-    <r>
-      <t>res://Assets/Music/Story/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>寻幽探胜</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
       <t>.mp3</t>
     </r>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>res://Assets/Background/black.png</t>
     <phoneticPr fontId="4"/>
   </si>
 </sst>
@@ -879,7 +824,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="標準" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1090,7 +1035,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:T20"/>
-  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="8.5" customWidth="1"/>
     <col min="2" max="2" width="6.625" bestFit="1" customWidth="1"/>
@@ -1108,7 +1053,7 @@
     <col min="19" max="20" width="10.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" s="20" customFormat="1" ht="18">
+    <row r="1" spans="1:20" s="20" customFormat="1">
       <c r="A1" s="15" t="s">
         <v>11</v>
       </c>
@@ -1170,7 +1115,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:20" s="20" customFormat="1" ht="18">
+    <row r="2" spans="1:20" s="20" customFormat="1">
       <c r="A2" s="24" t="s">
         <v>29</v>
       </c>
@@ -1500,13 +1445,13 @@
       <c r="E2" s="27"/>
       <c r="F2" s="27"/>
       <c r="G2" s="28" t="s">
+        <v>40</v>
+      </c>
+      <c r="H2" s="29" t="s">
         <v>38</v>
       </c>
-      <c r="H2" s="29" t="s">
+      <c r="I2" s="28" t="s">
         <v>39</v>
-      </c>
-      <c r="I2" s="28" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="3" spans="1:9">

--- a/DataTables/DetailText/剧情/000_05结局.xlsx
+++ b/DataTables/DetailText/剧情/000_05结局.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BDC0CDE-944B-4FB0-82F4-D48F11E3DBA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1F60AE5-37B1-4C60-BB57-B069FC2DBD67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story" sheetId="3" r:id="rId1"/>
@@ -1130,7 +1130,7 @@
         <v>33</v>
       </c>
       <c r="F2" s="22">
-        <v>1000</v>
+        <v>1000000</v>
       </c>
       <c r="G2" s="22"/>
       <c r="H2" s="22"/>

--- a/DataTables/DetailText/剧情/000_05结局.xlsx
+++ b/DataTables/DetailText/剧情/000_05结局.xlsx
@@ -1,22 +1,35 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Doctor\DataTables\DetailText\剧情\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1F60AE5-37B1-4C60-BB57-B069FC2DBD67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FCC44E1-4576-42F1-854E-D2FC5CEC9584}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story" sheetId="3" r:id="rId1"/>
     <sheet name="StoryLine" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -824,7 +837,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1035,7 +1048,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:T20"/>
-  <sheetFormatPr defaultRowHeight="18"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="8.5" customWidth="1"/>
     <col min="2" max="2" width="6.625" bestFit="1" customWidth="1"/>
@@ -1053,7 +1066,7 @@
     <col min="19" max="20" width="10.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" s="20" customFormat="1">
+    <row r="1" spans="1:20" s="20" customFormat="1" ht="18">
       <c r="A1" s="15" t="s">
         <v>11</v>
       </c>
@@ -1115,7 +1128,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:20" s="20" customFormat="1">
+    <row r="2" spans="1:20" s="20" customFormat="1" ht="18">
       <c r="A2" s="24" t="s">
         <v>29</v>
       </c>
@@ -1130,7 +1143,7 @@
         <v>33</v>
       </c>
       <c r="F2" s="22">
-        <v>1000000</v>
+        <v>6000000</v>
       </c>
       <c r="G2" s="22"/>
       <c r="H2" s="22"/>

--- a/DataTables/DetailText/剧情/000_05结局.xlsx
+++ b/DataTables/DetailText/剧情/000_05结局.xlsx
@@ -1,35 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FCC44E1-4576-42F1-854E-D2FC5CEC9584}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43B48574-D91D-48AE-96E6-48961020679B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story" sheetId="3" r:id="rId1"/>
     <sheet name="StoryLine" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
@@ -837,7 +824,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="標準" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1048,7 +1035,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:T20"/>
-  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="8.5" customWidth="1"/>
     <col min="2" max="2" width="6.625" bestFit="1" customWidth="1"/>
@@ -1066,7 +1053,7 @@
     <col min="19" max="20" width="10.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" s="20" customFormat="1" ht="18">
+    <row r="1" spans="1:20" s="20" customFormat="1">
       <c r="A1" s="15" t="s">
         <v>11</v>
       </c>
@@ -1128,7 +1115,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:20" s="20" customFormat="1" ht="18">
+    <row r="2" spans="1:20" s="20" customFormat="1">
       <c r="A2" s="24" t="s">
         <v>29</v>
       </c>
@@ -1143,7 +1130,7 @@
         <v>33</v>
       </c>
       <c r="F2" s="22">
-        <v>6000000</v>
+        <v>600000</v>
       </c>
       <c r="G2" s="22"/>
       <c r="H2" s="22"/>
